--- a/output/laminas_comunales/comunal_m_saldomigr_a_2023_metropolitana.xlsx
+++ b/output/laminas_comunales/comunal_m_saldomigr_a_2023_metropolitana.xlsx
@@ -1475,7 +1475,7 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Periodo 2019-2023. Escala de colores estandarizada a nivel nacional para todo el periodo.</t>
+          <t>Periodo 2019-2023. Escala comunal recortada a percentiles 3-97. Sobre umbral: San Miguel (7.525); Providencia (5.279); Colina (5.108); Lampa (13.488); Las Condes (3.678); Ñuñoa (11.779); Padre Hurtado (6.698); Paine (4.239); Buin (9.794). Bajo umbral: San Ramón (-5.548); Independencia (-9.194); Peñalolén (-13.850); Calera de Tango (-9.012); Santiago (-30.572); Puente Alto (-33.762); San Bernardo (-10.722); Cerro Navia (-8.302); Conchalí (-8.797); El Bosque (-11.255); Estación Central (-11.333); La Florida (-6.767); La Granja (-7.192); La Pintana (-10.800); Lo Espejo (-6.951); Lo Prado (-7.847); Maipú (-34.976); Pedro Aguirre Cerda (-7.489); Pudahuel (-12.291); Quilicura (-11.612); Quinta Normal (-9.043); Recoleta (-14.830); Renca (-9.203).</t>
         </is>
       </c>
     </row>

--- a/output/laminas_comunales/comunal_m_saldomigr_a_2023_metropolitana.xlsx
+++ b/output/laminas_comunales/comunal_m_saldomigr_a_2023_metropolitana.xlsx
@@ -1475,7 +1475,7 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Periodo 2019-2023. Escala comunal recortada a percentiles 3-97. Sobre umbral: San Miguel (7.525); Providencia (5.279); Colina (5.108); Lampa (13.488); Las Condes (3.678); Ñuñoa (11.779); Padre Hurtado (6.698); Paine (4.239); Buin (9.794). Bajo umbral: San Ramón (-5.548); Independencia (-9.194); Peñalolén (-13.850); Calera de Tango (-9.012); Santiago (-30.572); Puente Alto (-33.762); San Bernardo (-10.722); Cerro Navia (-8.302); Conchalí (-8.797); El Bosque (-11.255); Estación Central (-11.333); La Florida (-6.767); La Granja (-7.192); La Pintana (-10.800); Lo Espejo (-6.951); Lo Prado (-7.847); Maipú (-34.976); Pedro Aguirre Cerda (-7.489); Pudahuel (-12.291); Quilicura (-11.612); Quinta Normal (-9.043); Recoleta (-14.830); Renca (-9.203).</t>
+          <t>Periodo 2019-2023. Escala comunal recortada a percentiles 3-97. Sobre umbral: San Miguel (7.525); Providencia (5.279); Colina (5.108); Lampa (13.488); Las Condes (3.678); Ñuñoa (11.779); y 3 más. Bajo umbral: San Ramón (-5.548); Independencia (-9.194); Peñalolén (-13.850); Calera de Tango (-9.012); Santiago (-30.572); Puente Alto (-33.762); y 17 más.</t>
         </is>
       </c>
     </row>
